--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98050</v>
+        <v>98057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98057</v>
+        <v>98066</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98066</v>
+        <v>98074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98074</v>
+        <v>98076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54196-2022 artfynd.xlsx
+++ b/artfynd/A 54196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122095120</v>
       </c>
       <c r="B2" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>219790</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
